--- a/data/verify_output.xlsx
+++ b/data/verify_output.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,24 +489,40 @@
           <t>00384749</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PARRA HERNANDEZ</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>26-JUN-1986</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>REPUBLICA</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+          <t>FLORENCIA</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>171</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>26-JUN-1986</t>
+          <t>15-OCT-2004</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -516,23 +532,23 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>SRR kp o ea Dd
-ee eek Fe ee ee,
-(ES ONE PU
-| Ae: A o
-DIEGO ARMANDO 3/0 boa
-A, AI + + AE
-Ae SF er ae (ts ed =
-is A A o
-DE. CIA. &gt; |
-E=S FECHA De NAGIMiENTO 26-JUN-1986
-(ON (CAQUETA):  ' ;
-USO LUGAR DÉNACIMIENTO
-¿REPUBLICA DE COLOMBIA. ==
-a PARRA HERNAND a 0 a «e
-A A xs.
-| APELLIDOS! CS eee e E
-Bo aA</t>
+          <t xml:space="preserve">IDENTIFICACION PERSONAL u
+CEDULA DE CIUDADANIA — T -
+- NUMERO 1_117.&amp;-876 , »*i;ﬁ‘
+PARRA HERNANDEZ  2dní e a
+FECHA DE NACIMIENTO 26-JUN-1986
+FQ FLORENCIA
+í QD N (CAQUETA)
+&amp;) ) N LUGAR DE NACIMIENTO
+=7
+=) 1.71 B+ M
+7-%’—;:%2 ESTATURA G.S. RH SEXO
+15-OCT-2004 FLORENCIA . /.
+FECHA Y LUGAR DE EXPEDICION 45 m
+INDICE DERECHO EN REO ONcue s
+y ECC C ANE EA AE i A
+A-4400100-00384749-M-1117489876-20120628  0030392811A1 — 8081904776
+</t>
         </is>
       </c>
     </row>
@@ -551,29 +567,51 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>O+</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>440</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>09-DIC-1985</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>CARTAGO</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t xml:space="preserve">a RO Se, 2 Mate tiincdes’
-_ DENTIFICAC ‘PERSONAL. ~ or
-pa NA NA SS may
-ae ee SS
-Bit ed SN y ae era tt E y i ae tbo
-ities, cr a 2 y — ia ” ft E HA Ey } hia :
-[ga OR snes pu Tt AAR eee PO ke, Je
-«NUMERO ade REN ses A a a
-bar e 5d
-APREMIO 2 ~ ~The Ad E ae
-mes es ARA AE eS 2 stro
-yd is Pat gy’ E A SS </t>
+          <t xml:space="preserve">Wiy N E TE AR L e i a.1 _. - — -
+CAA 0T E | PE E NEE ENES - SA S B
+N = AEE B . * ..__Qº'.' e .¿..,3..*!¡,. PA _.4).¿_¿¿ - &amp; Ce £ |
+"" ACNTICIO AC I PERSON sa CREPUBLICA DS
+“fumero | EE YI U — =a =S
+1=&lt; aa —
+=D CARTAGO
+I Vs7 |
+ZN LUGAR DE NACIMIENTO
+— 1.76 O+ M
+e — ESTATURA — GS.RH SEXO
+— 09-DIC-1985 CARTAGO ".
+FECHA Y LUGAR DE EXPEDICION JJ
+INDICE DERECHO — REGISTRADOR NACIONAL
+197 1 NAUy 9 16 {50 N , WL E TUO N A NI el Y I. /
+E dA d 1a S VR LI Pt d aa eee y CA
+A-4400100-00202694-M-0016221480-20091210 0018859054A 1 8080589164
+</t>
         </is>
       </c>
     </row>
@@ -585,28 +623,44 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>17711201</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>67115951</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>OYOLA SABI</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>11-MAR-1983</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>166</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>04-ABR-2003</t>
+          <t>01-ABR-2003</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>CARTAGENA</t>
+          <t>CARTAGENA DE CHAIRA</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -614,23 +668,28 @@
           <t xml:space="preserve">REPUBLICA DE COLOMBIA
 IDENTIFICACION PERSONAL
 CEDULA DE CIUDADANIA
-| yen 17711201 na,
-OYOLA SAB! Am,
-MA _
-| a ES ‘ ut
-REPUBLICA DE COLOMBIA
-IDENTIFICACION PERSONAL
-CEDULA DE CIUDADANIA
-B
-| o 17711201
-OYOLA SAB! 7-4
-EONE! rr =
-I + TN OS —
-| UE | ad
-, de &gt; 4
-liars \ Quoc:
-VEGA - j y E € y” ; ~
-| A A </t>
+cc 17711001 b
+OYOLA SABI » —
+APELLIDOS ,
+7\ 1 Le 4
+…x( _ ;
+',/ | ,"
+e
+3 A
+! [ /)
+;¿;S;—%gaff FECHA DE NACIMIENTO 11-MAR-1983 ‘
+yf*'/%a'r'¿ztí¿iv:.;;u¿¿r',','-—rí¿s_¿(:¿_.%—'— LUGAR DE NACIMIENTO
+E 1.66 B+ M
+'Í'¿íffº¿vzi%“… ESTATURA G.S. AH sEXO
+a ZE 01.ABR2003 CARTAGENA DE CHAIRA
+uZ A 4-ABR- ! !
+_j? FECHA Y LUGAR DE EXPEDICION u_m___%&amp;;
+MDICE PERECIO ) ngfw....mw
+E;… 1.¡'_*'.[.I' ». ',Ac Lot \-"' ‘t'?| my l'i&amp;'¡..,' '-':0 ‘J'IP
+g RN
+P-4400300-67 115951-M-0017711201-20030702 00172031824 O1 122557565
+Powered by CamScanner
+</t>
         </is>
       </c>
     </row>
@@ -647,32 +706,59 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>24-ENE-2001</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>O+</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>16-ABR-2019</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>GARZON</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>e ON
-Goes UNG EPUB AG 3} &gt; COLOMBIA ee SI ee
-a IDENTIFICACION PERSONAL... cg ae Is cree
-a es E [Oe
-eS CU i
-¿PEDRO JOSE &gt; dello end ti
-NO e o io ci a
-RSS SN ena OR fade ee eae Suey e en Be a aa
-hodmius PAS
-E a La 2 es HEN uo fogs
-ASE as Oo po a ee ES Ss E “He
-ce A ICADPCOLOMBIA ==... 7
-| = IDENTI</t>
+          <t xml:space="preserve">— REPÚBLICADE COLOMBIA - |
+— - IDENTIFICACION PERSONAL. — — '
+= CÉDULA DE CIUDADANÍA E -
+- sovero . 1:006.801-709. y —
+- fedo foven .- MO
+;//-_"N\ FECHA DE nacimiento 24-ENE-2001
+7N FLORENCIA
+7 ﬁ\ (CAQUETA)
+ÓN
+/ N N N LUGAR DE NACIMIENTO
+— Ñ 1.60 — O+ M
+— ESTATURA G.S. RH SEXO
+AN 16-ABR-2019 GARZON
+, FECHA Y LUGAR DE EXPEDICION — | VM
+INDICE DERECHO REGISTRADORINACIONAL
+JUAN'CARLOS GALINDO VACHA
+it DI e NAZ R oLt L
+Ii‘ III “'h r ‘L“ r I4 I, Iﬁ' 1 " ] - 1| h 1 I ¡I. I'Iw '!’i}l I;. i "
+P-1903400-01082644-M-1006501709-20190710 0066217904A1 — 53258405
+</t>
         </is>
       </c>
     </row>
@@ -694,23 +780,15 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t xml:space="preserve">TZ
-EA a "a
-| RS
-lt a d a ie
-Pu &gt;
-is ae Fa
-y
-sey o TD Des DA Al 2 Rs Pe. &gt; E ay
-o ay ee
-ek Sf
-—_ .
-a
-: E Dio
-a Ger
-soem ee Se ae RE
-4 qe + eeu, da ae Rees
-"ad bi be ny Elo aa 4
+          <t xml:space="preserve">— E A DE DáNIA” — — = E-
+AR e ra NAe EE p
+. — - N [ ;
+- . Cn -r
+s E s DS eee e
+CRE = .-_ ñ TE NEZ Ae -
+mento - O7-NOV-1987 — )
+IIICEII.… S ,v'_“.‘ﬁ" X ¢ C i
+— . — o — —
 </t>
         </is>
       </c>
@@ -721,30 +799,60 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>00686132</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>POSADA ALFONSO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>IWÍ</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>12-JUN-2000</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>EL PAUJIL</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-  JOENTIFICAGIÓN PER a ee E
-PNR ni A : is
-o FOSO. oo E Es AS]
-Gree RENA TD de O Osc
-“RODRIGO a a OLIVERA. sae aoe
-= NOMBRE S » e A A LE z ns q A
-Sabot. PEE. &gt; "OS E
-a pe ay ¢ BES oa Be ee Se sra
-Fee o emer O ee Beene E RS e ens]
-o ME PUBLICA LALA i Poe A eee
-&lt;&lt;» IDENTIFICAL (PERSONAL = A y Ss
-&gt; CE</t>
+          <t xml:space="preserve">‘ ,ºí “¡.'Í“f 4 Jqﬁ&amp;f’(ft?ﬁf‘i&amp;iafif\:« e _; ' : : A _ S
+— IDBNTIFICACIONPERSONAL “ — ~
+... — -
+ME…) » 44 &lt;f E A B N O É o
+- POSADA ALFONSO — — a -
+- APELLIDOS . En — — …**'?*%5
+— e - u ;'IWÍ'V'* r a — M a e
+,;/ EC E’“‘s}’ — .. s — F N -
+ERAN A - . A7 ,
+" apgpyper "
+E— — ESTATURA — GS.RH SEXO
+EA 12-JUN-2000 EL PAUJIL _
+AN r S g — =
+FECHA Y LUGAR DE EXPEDICION l--
+INDICE DERECHO re REGISTRADOR NACIONAL
+T A AA AA AA CA TE PA
+A-4400100-00686132-M-0086333300-2015041 1 0043842169A 1 8083353535
+</t>
         </is>
       </c>
     </row>
@@ -763,15 +871,19 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>176</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -786,17 +898,29 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t xml:space="preserve">IDENTIFICACIÓN PERSONAL. a
-BASTIDAS ORTIZ. [E , PUE
-‘ &gt; © Ene y A a = hea |
-E &gt; eth eae oe O e a4 yo. á o. i
-e 5 5 5 5 EE NER NE ENE]
--=- IDENTIFICACIÓN PERSONAL. a
-See CÉDULA DE CIUDADANÍA | 3 E
-Eansos Boshidas.. ii
-nn ne eaneenInEaeeenseeeeneneemnememenememmaml
-Pies (CAQUETA) ~~ $
-EE 1.76 A A </t>
+          <t xml:space="preserve">REPUBLICA D&amp; COLOMBIA
+IDENTIFICACIÓN PERSONAL s
+' CéniiA DE CIUDADI NA l 1
+ua 1.006.521.73% | - &gt; —
+— BASTIDAS ORTIZ _
+D eo e G
+Dy — * !__._.. ; .º__"_'_:.:.... .
+J Boshidas é:*.:i'h
+o “_ l , r K . , -
+E sa FECHA 02 NACUMENTO 19-DIC-2000 -
+S (CAQUETA)
+ER b LUGAR DE NACIMENTO
+ra 1.76 A+ M
+. e ESTATURA as AH spxo
+=== 30-ENE-2019 FLORENCIA
+FECHA Y LUGAR OE ExPEDICION — | Wi
+L ENEO "e
+an "
+‘ ’1?’1' 6 '2:' e "! B 1TT AR L\ B RS MR
+".j‘, .'. I“, ,’.:’\ y‘|,.“ .;_,31¿."*1:.(_ lí¡'.;;.,!'!;..'_.¡&lt; .':¡-j_t.l.
+':, k' ).:.l' _!i_ltj"sf.: r '..‘..'x\cu:.!:‘r:q.l.:l ,_1_":“1 1.:.'-_'1... ; '.“
+4400100 01064009 M- 1006521 729-20190777 00848550404 1 0088327959
+</t>
         </is>
       </c>
     </row>
@@ -812,31 +936,52 @@
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ TOVAR CARLOS EDWIN</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>07-NOV-1996</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>07-NOV-1996</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O DULA DE- CIUDADANIA - Xx Jae |
-TA te = ¿E E A es
-ae a
-Pron &gt; ai ee = . pa y,
-E aa: Y. Y ME A A
-REPUBLICA DE COLOMBIA
-IDENTIFICACIÓN PERSONAL |
-DULADECIUDADANIA; = a
-RES &gt; DE o
-MISA RES de A
-LIGA py EA
-— A : y A tio MARI
-y aa po
-EN: S y A DEN IENTO BA h o 4
-P-AA02200-00653467:M-1110586245-201412</t>
+          <t xml:space="preserve">REPUBLICA DE COLOMBIA
+IDENTIFICACION PERSONAL
+CEDULA DE CIUDADANIA
+o 1.119,586.245
+RODRIGUEZ TOVAR ...
+CARLOS EDWIN — AO
+NOMBRES / - N i
+~ . a 3 '-"';. a .
+orldSE . ¿
+FIRMA , a- EE
+_' w .f."x';;r "
+_A
+_;… FECHA DE NACIMIENTO — 07-NOV-1996
+NE LUGAR DE NACIMIENTO
+= ESTATURA — GS.RH SEXO
+rewvmf__  EXPEDICION W *
+“a “ay U .¿.;'_r¡"_¡_*h'j".(-“ - ‘-"1".}:5.‘; % &lt; WA VAT A de A
+P-4402200-00653467-M-1119586245-20141224  0042108566A 1 — 42036739
+Powered by CamScanner
+</t>
         </is>
       </c>
     </row>
@@ -848,7 +993,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>127070363</t>
+          <t>1127070363</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -858,38 +1003,53 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>JHON JAMEZ COL M</t>
+          <t>JHON JAMEZ</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>O-</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>11-JUN-2004</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>GARZON</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ú e
-cubana da mm REPUBLICA DE COLOMBIA
-“ Apellidos NUIP 1,127.070.363
+          <t xml:space="preserve">I ,
+CUDADANA — Man — REPUBLICA DE COLOMBIA
+" Apellidos NUIP 1.127.070.363
 ANDRADE CADENA
-Nombres.
-JHON JAMEZ E
-COL 1.66 Mo y td
-Fecha de nacimiento &amp;&gt;GS. Ry
-07 JUN 1986 —O- AA
-Feche y ugar de expedición ent
-11 JUN 2004; VILLAGARZON ~_
-Frma I ect de engin &lt;——&gt; )
-tz 16 AGO 2033 RAE E
-p 2 =) /
-Ú e
-cubana </t>
+i 3 mgi: JAMEZ
+Nacionalidad Estatura Sexo 2
+E F(íc?aLde nacimiento “ G1é66 ¥ _
+- 07 JUN 19868 O-
+| VILLAGARZON (PUTUMAYO) -
+Fecha y lugar de expedición
+11 JUN 2004, VILLAGARZON
+A 2
+- íº¿éá a
+E E
+' g% *Í,íf¿í?&amp;%f
+Te
+N . REGISTRADOR NACIONAL Ok -“‘5""", 1
+Alexander Vega Rocha
+ICCOLO29968127464030&lt;&lt;&lt;&lt;&lt;&lt;&lt;&lt;&lt;&lt;
+8606073M3308165C0L1127070363&lt;5
+ANDRADE&lt;CADENA&lt;&lt;JHON&lt;JAMEZ&lt;&lt;&lt;&lt;
+L 5
+</t>
         </is>
       </c>
     </row>
@@ -901,7 +1061,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1117553913</t>
+          <t>117553913</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -915,14 +1075,13 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t xml:space="preserve">i 4 ne en 0 ii po a
-| +" REPÚBLICA DE COLOMBIA &gt; Wie
-WOR 1.117. 553.913 "E
-4 ei af ‘a ». - = pino: y
-| + CÉDULA DE CIUDADANÍA ~ er E 4
-na ER ro e
-¡acto E
-e E RR ee
+          <t xml:space="preserve">REPÚBLICA DE COLOMBIA
+IDENTIFICACIÓN PERSONAL
+CÉDULA DE CIUDADANÍA
+NUWERO 4 117.553.913 a
+-' GUARNIZO REYES |
+- PAULA ANDREA a
+@ 4 —
 </t>
         </is>
       </c>
@@ -933,33 +1092,38 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>01007886</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mes a Fo AF iso == e
-Ch £ d AR a E 3
-= ME Da y A “ ma ¡pt Rs &lt; “hee
-ee x y : E
-= al = dé |
-iz ; O ER Pe
-a &gt; &gt; a r ohm —e rg &gt; E o “e 4 4 :
-- ~"e che = Z at 2 = l. Ae .
-— Tee ee * de o Asie
-&gt; a a
-“4 yale ava a a | : 4 e «l 1 a
-A i} , fi A Ay ay, ij a a? ae K he Py =e
-Tid hoe Y war) PA) A a
-</t>
-        </is>
+      <c r="L12">
+        <f>~ a E
+F&amp;wºan?m 28-JUL-1999 |
+NEIVA - £ |
+ESTATURA GS AH SEXD
+; — 02-AGO-2017 FLORENCIA | '
+3 FECHA Y LOGHA DE EXPERCION — | yp |
+. — f
+| AA EA S A 1" 87 _. —_
+aA T A TA TNE o 19 A :.¡'¡.'.1.»10. PE
+" « J‘ “ - ..—. . h ”'¡._ T 11 4l » . s t'_. y" Y t..
+P-4400100-01007886-F-111755391 3-70180507 00610532204 1 PIRAZ242571
+</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -970,11 +1134,15 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>077868396</t>
+          <t>1077868396</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>WILMER ALEXANDER</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -982,20 +1150,23 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13">
-        <f>, . REPUBLICA DE COLOMBIA |
-"ys ADENTIFICACION PERSONAL
-0 CEDULA DE CIUDADANIA
-~ numero 1,077.868.396
-_.©CHAVARROGARAVITO, +. ay
-e ee a AAA RR
-=) + REPUBLICA DE COLOMBIA |
-y.  IDENTIFICACION PERSONAL
-E: CEDULA DE CIUDADANIA
-“numero 1,077.868.396
-AO o MI so eee E a
-NipMgres © ih 7 dl E E MA. </f>
-        <v/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aa TE 5 TA E ,
++ . REPUBLICA DE COLOMBIA ¿
+. IDENTIFICACION PERSONAL
+' CEDULA DE CIUDADANIA
+— numeño 1.077.868.396
+CHAVARRO GARAVITO e ;áíg,.
+— APELLIDOS Z_ - |
+- WILMER ALEXANDER-- * —
+“ | , - = a - S -
+m ,e a
+DSTÉ 4 Cuavarto — U Y.
+4 — Ta. E A
+Powered by CamScanner
+</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1016,42 +1187,41 @@
           <t>08-JUL-1994</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>JUL</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>08-JUL-1994</t>
+          <t>17-JUL-2012</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>GUESS</t>
+          <t>GARZON</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2 AS FECHA.DE NACIMIENTO '08-JUL-1994
-GUESS — GARZON E
-Wy ] ASS LUGAR DE NACIMIENTO wie
-LZ ESTATURA * -G.S. RH SEXO. + i:
-Wy wees &lt;= FECHA.DE NACIMIENTO 08-JUL-1994
-PINES
-RPG ES RR GARZON E AE
-Y) Wife SS SIN q
-a E Vey : SE (HUILA). . se
-Y SS LUGAR DE NACIMIENTO St
-Za ESTATURA *. -G.S. RH SEXO, +.
-L</t>
+          <t xml:space="preserve">r A k
+////'/ÍCÍ';Í;Í%—%Ú&amp; FECHA.DE NACIMIENTO 08-JUL-1994
+v,/%/////f/“áºº&amp;xw% (HUILA) . ,
+///%%t&amp;‘i\\\\sg LUGAR DE NACIMIENTO *
+º—í%”//áí—i%&amp;:;…—jéa ESTATURA “. G.S.RH SEXO — -
+AZ as — 17-JUL-2012 GARZON | D
+FECHA Y LUGAR DE EXPEDICION l/ Y -
+INDICE DERECHO * CARLOS ARIEL SÁNCHEZ TORRES |
+aPe LEBYE Dr 3 O B U R O , NE » Ea A
+2M CA raD R R O]
+-'l' ,'5 " Y ?’l 'Ef“ .Án¡ .#-“’ ',¡4á'% ná(&amp;*
+g A ot A et ONO bl ke )
+P-1903400-00397062-M-1077868396-20120905 . — “0030988239A 1 38194069 —
+Powered by @ CamScanner
+</t>
         </is>
       </c>
     </row>
@@ -1064,38 +1234,56 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>02-SEP-1987</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>MACARENA</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>07</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>14-ENE-2006</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>MACARENA</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+
-o ES ta of . q fe Hori +e * a
-AA 4 És A : 7
-- == A i e ñ 5 At Ate x sell
-Su, ee) POEs |
-Pago ILICA DE
-e NTIFICAC ÓN
-5 Pa eS.
-ho ; e
-$ Jr E te A ~
-DIANAPAOLA
-| A _ a a E vi AE
-&gt; 3
-| a a See
-7 er, i fi se AE o
-| A GS. RH SEXO
-| FECHA Y L EXPEDICIÓN | wily
-E hh PLA he o Al o 0 07% bi. a" 3 |
-7 a a f</t>
+          <t xml:space="preserve">B %: COLOMBIA
+. N PERSONAL
+C CEDULA DE CIUDADANIA
+— RODRIGUEZ IMBUS — —
+_ .
+e o S*
+(/;A PAOLA "
+-
+‘ FECHA DE NACIMIENTO 02-SEP-1987
+LA MACARENA
+| (META)
+LUGAR DE NACIMIENTO
+| 1.54 A+ F
+11. ] ESTATURA G.S, AH SEXO
+14-ENE-2006 LA MACARENA
+FECHA Y LUGAR DE EXPEDICIÓN Wi u
+</t>
         </is>
       </c>
     </row>
@@ -1112,10 +1300,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>MONTAÑA LOZADA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>JONATHAN</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
@@ -1125,15 +1317,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t xml:space="preserve">REPUBLICA DE COLOMBIA A
+          <t xml:space="preserve">REPUBLICA DE COLOMBIA
 IDENTIFICACION PERSONAL
-CEDULA DE CIUDADANIA $
-MONTAÑA LOZADA... E. |
-REPUBLICA DE COLOMBIA E
-IDENTIFICACION PERSONAL
-CEDULA DE CIUDADANIA 4
-xumero  1.117.521.669 2. fi E
-A O PA ee
+CEDULA DE CIUDADANIA
+numERO — 1.117.521.669 '
+MONTAÑA LOZADA =
+APELLIDOS
+JONATHAN E
+NOMBRES
+… &lt;
+— e p v — %
+Powered by aCamScanner
 </t>
         </is>
       </c>
@@ -1146,7 +1340,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4400100</t>
+          <t>00218221</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -1158,42 +1352,33 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FLORENCIA</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>16-NOV-1991</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>FLORENCIA</t>
-        </is>
-      </c>
+          <t>EUNO</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>“ EUAN FECHA DE NACIMIENTO 16-NOV-1991
-¿AÑOS FLORENCIA | “fae
-il ON NN (CAQUETA) si 7
-j AS | NN LUGAR DE/NAGIMIENTO* y “eee |
-: Sait eee ESTATURA [11 OS, RH SEXO. |
-oir ros Romer 97. NOV.DARO ELORENCIA A
-4 SS ome ae 16-NOV-1991
-IAS NS 176 00 O+ +. M 7
-OS ESTATURA (ls 0,5, AH SEXO |
-AN e 27-NOV-200</t>
+          <t xml:space="preserve">NNN FECHA DE NACIMIENTO 16-NOV-1991
+EUNO (CAQUETA) _
+¡'v*&amp;¡l¿&amp;&amp;¿&amp;;_" ¡…XKX N LUGAR DE NACIMIENTO
+MN 176 0+ M
+NNO 27-NOV-2009 FLORENCIA
+FECHA Y LUGAR DE EXPEDlCloy,,M/M/oﬁfL -
+INDICE DERECHO R REGISTRADOR NACIONAL
+! CARLOS ARIEL SÁNCHEZ TORRES
+TNEO Rt T U R A A
+P-4400100-00218221-M-1117521669-20100225 0021293834A 1 30927431 j
+4
+Powered by @CamScanner
+</t>
         </is>
       </c>
     </row>
@@ -1205,29 +1390,49 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>001803924</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+          <t>00180324</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>GOMEZ TORRES</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>JHON FREDDY</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>19-AGO-1968</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>PITALITO</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>O+</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>25-JUN-1987</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>14-AGO-1968</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>PITALITO</t>
@@ -1235,22 +1440,35 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>. REPUBLICA DE COLOMBIA
+          <t xml:space="preserve">_ REPUBLICA DE COLOMBIA
 IDENTIFICACION PERSONAL
 CEDULA DE CIUDADANIA
-ee ee ae —_ * AE * i,
-. REPUBLICA DE COLOMBIA
-IDENTIFICACION PERSONAL
-CEDULA DE CIUDADANIA
-ax wee’ ie “
-ec A oe mt, A L fe L
-i ZL oy &lt;_&lt;
-ta ' — 4 A o - y Cll
-FEcHA DE Nacimignro  14-AGO-1968
-PITALITO.
+NuUMERO 12234223
+GOMEZ TORRES
+_ APELLIDOS _A
+JHON FREDDY v
+| / - s 1 = . -
+_r/ ¡ l n ( 4
+AL "—
+4 1 A —
+,’) A… ".;..Í.":' -". :'
+: ,—',7" \ + .&amp;&amp;wv . 7—*_ 7 ,:
+FECHA DE NACIMIENTO — 19-AGO-1968
+PITALITO
 (HUILA)
 LUGAR DE NACIMIENTO
-1</t>
+. 1.67 O+ M
+… ESTATURA G.S AH sexo
+D ra ae 25-JUN-1987 PITALITO L
+FECHA Y LUGAR DE EXPEDICION fouken g A==y =~
+NOICE DERECHO MEGISTRACOR NACONAL
+CAR OS AMEL Mimc=a ? —amES
+" \i " ’]‘:\”‘ 1 4 .
+Di ’d‘.: “ (a'l': " “-«:". E "s ..¡ " ;. " "‘-‘ -.' " .'.u
+U NE -'.?'¡-.¡_“_'?_¡ 0AM e S &amp; .{c\-‘ AN '
+? 1A ":."".‘."' ;‘- 4 .)'4"‘, 'I‘:{:' :l ;J'{\.‘ _.\Z“!.‘:, "r AO ¿“.4".- a
+A-1906100-00180324-M-0012234223- 20090922 00164410004 1 — 7130100983
+</t>
         </is>
       </c>
     </row>
@@ -1265,39 +1483,61 @@
           <t>1110487315</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SANCHEZ PINZON</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ANDREA PATRICIA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>08-JUL-1989</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>BOGOTA</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>O+</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>10-AGO-2007</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t>IBAGUE</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>suas, wm REPUBLICA DE COLOMBIA
-————— NUIP 1.110.487.315
-IO, — SANCHEZPINZON
-sj _ ANDREA PATRICIA
-Aa — ,
-f= = COL 162  F
-== = Fecha de nacimiento. GS. ]
-E — ee: 08 JUL 1989 O+ :
-a — Lugar de nacimi
-= = BOGOTA D.C. (CUNDINAMARCA)
-= Fecha y lugar de expedici
-E 10 AGO 2007, IBAGUE -
-Male. Ica ——— |
-CÉD</t>
+          <t xml:space="preserve">CUPADANA — m  REPUBLICA DE COLOMBIA
+— — Apellidos NUIP 1.110.487.315
+SANCHEZ PINZON
+Nombres
+' ANDREA PATRICIA
+Nacionalidad Estatura Sexo
+.COL : | V
+Fecha de nacimiento  G.S. .
+08 JUL 1989 O+
+Lugar de nacimiento '
+BOGOTA D.C. (CUNDINAMARCA)
+Fecha y lugat de expedici
+10 AGO 2007, IBAGUE -
+Anerea Sdef el — —e U
+' 5 Ry
+</t>
         </is>
       </c>
     </row>
@@ -1319,8 +1559,8 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t xml:space="preserve">i ’
-‘ 7 d |
+          <t xml:space="preserve">|
+L
 </t>
         </is>
       </c>
@@ -1333,35 +1573,50 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>117811433</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+          <t>1117811433</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>FIERRO GUACA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ERIKA JULIANA</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t xml:space="preserve">AZ a REPUBLICA DE COLOMBIA
-y Apemaos NUIP 1,117.811.433
+          <t xml:space="preserve">N - REPUBLICA DE COLOMBIA
+P— NUIP 1.117.811.433
 FIERRO GUACA
-| HKÉ]Á a4 ||
-BZ =e REPUBLICA DE COLOMBIA
-a Apatneee NUIP 1.117.811.4393
-_ FIERRO GUACA
-Nombres
-| E cal 1858 + Y
-Ed. . :
-il Pi ga’ de nacHmentc .
-- (CAQUETA)
-. Fecha y lugar de expedición F
-10 ABR 2024, SAN VICENTE DEL CAGUAN
-Bal </t>
+Nomby e
+ERIKA JULIANA
+Nacion. 087 - stah N
+COL 185 F
+SAN VICENTE DEL CAGUAN
+(CAQUETA) a
+10 ABR 2024. SAN VICENTE DEL CAGUAN
+"E Ea ;&amp;LW*‘O' 10 ABR 2034
+&amp;
+Powered by CamScanner
+</t>
         </is>
       </c>
     </row>
@@ -1371,11 +1626,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>62484410</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
@@ -1387,12 +1638,12 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>wee
-HA "ee ~~" Ah Oe ER ee FS yh IA eee E ql Sin Soeur. ON eps AA a, RE 3 $ =
-A Ro ps etl Oni Lunar a nie ee Ot Ne PA Sa ess oi enor ° pa! E
-OE Ne ay ao ed ae Peres MBS A oe ea RS aired meer eae El ETA alts A : 2
-Ln A e IA EO tow, A We a gia EA ALTO ESSE IE vee za En 2c y= ed
-O o Mao Sa: AA NOI</t>
+          <t xml:space="preserve">I
+Sr
+: UL A s T
+- n y
+Powered by CamScanner
+</t>
         </is>
       </c>
     </row>
@@ -1407,35 +1658,66 @@
           <t>1117234502</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SEPULVEDA SILVESTRE</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>13-ABR-1990</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>MILAN</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>O+</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>165</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>13-AGO-2008</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>MILAN</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>_cupacanis)( a REPUBLICA DE COLOMBIA
-un Apellidos NUIP 1.117.234.502
-(5 E SEPULVEDA SILVESTRE
-E ==3 a &gt; = : Nombres 7
-: = — — = = Nacionalidad Estatura Sexo a)
-) GEDODADES y VS VRE PAL eS t Te A, \
-_ cuoacane a REPUBLICA DE COLOMBIA
-(By ”“_ZZ_=™ z= SEPULVEDA SILVESTRE
-E == =. = = Nombres
-a a. EI</t>
+          <t xml:space="preserve">CEDULA DE | |
+— CIUDADANA - E REPUBLICA DE COLOMBIA
+= Apelidos NUIP 1.117.234.502
+=8 — - SEPULVEDA SILVESTRE
+— = — — Nombres |
+' ::: ' _ Nacionalidad Estatura Sexo
+— - COL 1.65 M
+3 a == = Fecha de nacimiento GS.
+== — 13ABR 1990 O+
+= — — — = Lugar de nacimiento
+?:Í;;—__——%_ '¿ F = = - Fecha y lugar de expedicion 6
+- 13 AGO 2008, MILAN
+Firma_““ T DO - Fecha de expiración !
+@f 25 ABR 2033 | *
+h al
+Powered by CamScanner
+</t>
         </is>
       </c>
     </row>
@@ -1447,11 +1729,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0233664152</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+          <t>1117234502</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SEPULVEDA SILVESTRE</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>EINER</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
@@ -1461,19 +1751,16 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t xml:space="preserve">-CO nw. A = a ee .
-3 etek ee
-S | | Bo eS Oe sks
-S a O
-230) pw ADE O
-f CO ——— |
-E o
-As
-wy Be
-==" NACIONAL EA
-1CCOLO23366415044016&lt;&lt;&lt;&lt;&lt;&lt;&lt;&lt;&lt;&lt;
-9004137M3304259C0L1117234502&lt;9
+          <t xml:space="preserve">M aaa h
+A CA
+- a
+5 S e
+. —
+. RE&amp;&amp;;E&amp;?QEI;Q h;A;(%I ONAL %?&amp;?E*&amp;%?%g&amp;?á
+ICCOLO23366415044016&lt;&lt;&lt;&lt;&lt;&lt;&lt;&lt;&lt;&lt;
+2004137M3304259COL1117234502&lt;9
 SEPULVEDA&lt;SILVESTRE&lt;&lt;EINER&lt;&lt;&lt;&lt;
+Powered by (8 CamScanner
 </t>
         </is>
       </c>
@@ -1490,29 +1777,33 @@
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>OSCAR LEONARDO VMBRES AL FIRMÁ</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>17-NOV-1987</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>FLORENCIA</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
           <t>19-ENE-2006</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>PES</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>19-ENE-2006</t>
-        </is>
-      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>FLORENCIA</t>
@@ -1520,23 +1811,29 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>a S
-OSCAR LEONARDO == pes
-JS &lt;= ES é E
-A NANO
-— IDENTIFICACION PERSONAL i
-i CEDULA DE CIUDADANIA : 7
-id A 4
-APELLIDOS. 6 MAS ¿ES E
-sc / pees E
-a ene
-_ ETT,
-E ASE
-EWN FECHA DENAGIMIENTO » 17=NOV-1987
-28 (CAQUETA). NS E
-YAWN LUGAR DE NACIMIENTO
-PES ESTATURA |) GS. AH SEXO
-Se 19-ENE-2006 FLORENCIA _ A</t>
+          <t xml:space="preserve">ii
+REPUBLICA DE COLOMBIA
+IDENTIFICACION PERSONAL
+CEDULA DE CIUDADANIA
+nuvero 1.117.497.954 W
+APELLIDOS . ,g?',?.. s ]
+— OSCAR LEONARDO - -
+../N';)VMBRES a«‘*‘ |
+al FIRMÁ —
+n oo ee —
+:\;g\\‘\ FECHA E NACIMIENTO — 17-NOV-1987
+=d FLORENCIA
+Á J (CAQUETA)
+Z IN LUGAR DE NACIMIENTO
+ZNN
+D ESTATURA G.S. RH SEXO
+— 19-ENE-2006 FLORENCIA /
+FECHA Y LUGAR DE EXPEDICION - l-7//=37
+INDICE DERECHO ea T a o
+" QJ y L) '3… 1 aCO " f"'-""gf' &amp; .f'J}' M
+A-4400100-00316296-M-1117497954-20110725 — 0027540280A 1 — 8081425496
+CamScanner
+</t>
         </is>
       </c>
     </row>
@@ -1553,23 +1850,52 @@
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>31-AGO-1991</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>01-SEP-2009</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>PALERMO</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t xml:space="preserve">bs UMERO ( i is &gt; api =. 3 ore ty a
-Hi ~ = A do A )
-Be ae. NS
-4 4 z | Pi a 4 5 a A
-y EN ; - a ¿a E
-. : ees eee EBS IICA ALI a ar
-INDICE DERECHO ÓN per ae RADOR NACIÓN |
-ss . OS AR IEL SÁNCHEZ
+          <t xml:space="preserve">| 2 . T- ME CD E J-
+¡ aproNo JAVIER / — M |
+, _¡:* FECHA DE NACIMIENTO 31-AGO-1991
+“ﬂi&amp;j‘i‘\ N LUGAR DE NACIMIENTO
+— 1.64 A+ M
+,ng E ESTATURA G.S. RH SEXO
+n 01-SEP-2009 PALERMO L
+FECHA Y LUGAR DE EXPEDICION Le=tr/=*=3
+INDICE DERECHO REGISTRADOR NACIONAL
+CARLOS ARIEL SÁNCHEZ TORRES
+[ + A D | N w KD b
+A-1905500-00625073-M-1080293667-20140919 0040101383A 1 41624290 —
+N —]]]———ZL AA E E
 </t>
         </is>
       </c>
@@ -1580,11 +1906,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1117499336</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
@@ -1596,18 +1918,8 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t xml:space="preserve">ee tm | REPUBLICA DE COLUMBIA
-de MUI? 1.117.499.336
-ALDANA BOHORQUEZ
-A E Y
-TD es HEPUBLILA DE COLOMBIA
-| des MUI? 1.117499.336
-ALDANA BOHORQUEZ
-Fi COL 1 +
-— = de Y 08 MAYO 1987 Os
-ZL FLORENCIA (CAQUETA) yi
-TS MAYO 2005, FLORENCIA
-pa ases Y
+          <t xml:space="preserve">o
+Powered by CamScanner
 </t>
         </is>
       </c>
@@ -1630,14 +1942,8 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t xml:space="preserve">*. NS
-CM “esas a”, ty Aa
-o y A ‘
-; ES : oy ao 5 Bb
-ro He AVI ES
-1CCOLO13470432444001&lt;&lt;&lt;&lt;&lt;&lt;&lt;&lt;&lt;&lt;
-8705080F3302244C0L1117493336&lt;3
-ALDANAX&lt;BOHORQUEZ7Z&lt;CLIDACYASMINE
+          <t xml:space="preserve">.
+Powered by CamScanner
 </t>
         </is>
       </c>
@@ -1650,15 +1956,19 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>79665698</t>
+          <t>796065698</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SAMUEL FERNANDO WE II</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>URREA RAMIREZ</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>SAMUEL FERNANDO</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
@@ -1668,18 +1978,17 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t xml:space="preserve">REPUBLICA DE COLOMBIA | |
-y IDENTIFICACION PERSONAL |
-CEDULA DE CIUDADANIA J
-| NUMERO 79.665.698 ff S ón E
-URREA RAMIREZ 7. E
-REPUBLICA DE COLOMBIA 24
+          <t xml:space="preserve">REPUBLICA DE COLOMBIA
 IDENTIFICACION PERSONAL |
-: CEDULA DE CIUDADANIA - y
--  URREA RAMIREZ E j
-APELLIDOS a e, A
-- . SAMUEL FERNANDO verse Ne) A Pa f
-NOMBRES _ § pete. </t>
+CEDULA DE CIUDADANIA —
+— nuvero 79.6065.698 ii
+— URREA RAMIREZ e E
+' APELLIDOS | i‘i"' -
+[ SAMUEL FERNANDO s |
+. NOMBRES |
+O Sarre! Lrrendo ey ‘ — .-
+| | FIRMA É
+</t>
         </is>
       </c>
     </row>
@@ -1691,22 +2000,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>4401000</t>
+          <t>00241833</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>ENE</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>21-ENE-1973</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>175</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1721,21 +2034,29 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>y LN PA DE Nacimiento 21*ENE-1973
-PEN PITAL
-OE IN LUGAR DE NACIMIENTO
-&lt;=
-A ESTATURA G.S. RH SEXO
-DAS 06-JUN-1991 BORNTA n »
-= aN . FECHA DE NACIMIENTO 21 ENE 1973
-= at \\ PITAL
-SN HUILA
-Yipes ES 2) LUGAR DE NACIMIENTO
-Prada AA LATA &gt;
-SAA ae
-= A ESTATURA G.S. RH SEXO
-AA 06-JUN-1991 BOGOTA p.c 7
-FECH</t>
+          <t xml:space="preserve">i A/'i\:—bx N
+| ;‘5 % N FECHA DE NACIMIENTO 21-ENE-1973
+Á N PITAL
+5 -- @’)‘\,\W $ (HUILA)
+/f/(¡k%;,% \\ LUGAR DE NACIMIENTO
+A ‘;'ff,\.." N
+1.75 A+ M
+W ESTATURA G.S. AH SEXO
+P 06-JUN-1991 BOGOTA D.C /
+' FECHA Y LUGAR DE EXPEDICION --7
+6i INDICE DERECHO REGISTRADOR NACIONAL
+u CARLOS ARIEL SANCHEZ TORRES
+E; I II 1! 5 1. lb ] " lI ; l J 1 1 'l 1 P ll
+A NA ra EE AO O PRE E E
+, ' ] b f y T y
+'J ( Y ; Jq(‘lll’l ( l{ i ¡tg ll ' : Lfll¡f
+| | ] ] ' } 1 ;
+; AO A bel L O el A e ¿Í
+1 y L} 4' l &amp;
+J Í.¡.'¿' '-?5'1 P? A -'¿í.ºj¿plf'l AE J( 3’51"1 H-
+' A-4401000-00241833-M-0079665698-20100618 0022355894A 1 33406062
+Powered by @CamScanner
+</t>
         </is>
       </c>
     </row>
@@ -1747,45 +2068,53 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>41409461</t>
+          <t>1110451846</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>O+</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>05-ABR-1987</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>STR</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t xml:space="preserve">AE PUB UICA DE COLOMBLA
-¡DENT vw ¡CACIÓN Penson
-CEDUL 4 DE UD ADAni
-wan) 4.1 409.461 846
-ALDANAVERA Y
-ancy Ane pa ‘
-Ñ IN . s "
-\ MARIA EUGENIA y. Set
-aye" " e p
-AE PUB UICA DÉ COLOMBLA
-¡DENT vw ¡CACIÓN PERSONAY
-cEDU ADE UD ADAni
-saat 11 40.461 846
-ALDANA yÉERA A
-Ao pa ‘
-MARIA EUGENIA ao y
-ayer e A
+          <t xml:space="preserve">REPUBLICA DE COLOMBIA
+IDEHTIFICACION PERSOMNAL
+CEDULA DE CIUDADANIN.
+PO a ra 1 -1 10.461 .846
+ALDANA VERA -
+TR 2 ". Y
+s A
+A \ 5 o ,
+'l/ ‘MARII\ EUGENIA — ¡r:í'o
+, A‘ A ra e *
+K | ' ( ¿E
+“ Mnu&amp;m,&amp;u — ;
+— L f_T—L
+¿gé.;¡ºífg,_ FECIA DE nacIMIENTO. OS-ABR-1987
+vjé_“¡rf¿) ae ALGECIRAS
+P £ . (HUILA)
+R S g A LuSAN Ne NACIMIENTO
+BNO 1.61 o+ — F
+¿*ff,;_:f¡ ESTATUNA 05 AN SEX0
+= — 20-JUL-2005 IBAGUE
+e FECHA Y LUGAN DL EXPERICION Ofáí.?í'.;)___
+INDICE DERALCHE nEGSTAADOS …ví:c¿ouu
+y á _á b E'!, EUN m i / q
+62900100 63141 107-5-1110451846 20051212 DISADOS1454 97 1no2canas ¡
+Escaneado con CamScanner
 </t>
         </is>
       </c>
@@ -1798,11 +2127,19 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>40038064</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+          <t>1003806124</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ONOV</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
@@ -1812,17 +2149,13 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CÉDULA DE R PU LIA ME AALARAD »)
-CIUDADANIA = 6 6©N E U EUA JE GULUIVIE A ñ
-A eos ES s Koide Ror (Boe B57 . (aa
-pS its, FT NUI? 4.003.806..4.
-3 = = y AMÓ ca LE &gt; A y So eee - See
-= EA ee MG NS. AOS A E
-= ess FOO" $ DROS: O —— f
-= O ==
-E =&gt; EIA E ES
-Firma 1 Y eAoha ASAS LS = AN
-NTRA NAAA 4 NR LT</t>
+          <t xml:space="preserve">CÉDULA DE 1 ! | " N
+CIUDADANIA — al  REPU BLLGA DE COLQMB#A
+4 ii m NUIP 1.003.806.124
+o2NOV2001 0+ — — — -
+rr =D E
+b | | D iy it 8 DA N - —
+</t>
         </is>
       </c>
     </row>
@@ -1842,31 +2175,24 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CIUDADANÍA HEPUBLIL E GULUIVIDIA |
-eases a ió Apellidos — - NUIP 1.117.266.865
-añ MUÑOZ BARRETO |
-—— i i AS a Nombms. e.
-E a E Nacionalidad Estatura O a
-o = = «SC MUNOZ BARRETO he
-=D E + Nombres S :
-&gt; CATAL o Be t
-SSE E eg fi = ae ‘Seer aay . , o : 3
-¡ÑO = Nacionalidad : Estatura Sexo AN
-| «2 « eas</t>
+          <t xml:space="preserve">CÉDULA DE | í |
+cuDaDANA — Ms REPUBLICA DE COLOMBIA
+Ae a Apelidos NUIF 1.117.266.865
+— ia - MUÑOZBARRETO |
+= 2 ' Í Nacionelidad Estatura Sexo
+1 “E - . = — Fechadenacimiento  G.S. -
+— N C Lugardenacimiento - A
+= Fechay_lugar‘de expedicion
+'W'"tw"’,f-;echa de expiración &lt; — — —
+¿% “ 23 ENE 2035 N *
+Powered by CamScanner
+</t>
         </is>
       </c>
     </row>
@@ -1876,9 +2202,21 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1117266865</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>MUNOZ BARRETO</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NATALI</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
@@ -1888,19 +2226,15 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>co Olin Sa Ade de). oe ' j
-A Fas he
-&gt; ; ER ‘ bn &lt;= Sen ma
-WERE Cee dat ah
-fa ig i A at E ae ee A 3 del
-E ls e A A ¢ $ hn DS So? Lae E y 7 pS y
-“CO Olean Sa RA Ae “ie
-= | eas Rae
-3 | Spang cette oe
-&gt; ee Ame sey pitts
-' 1CCOLO72680478644024&lt;&lt;&lt;&lt;&lt;&lt;&lt;&lt;&lt;&lt;
-9512243F3501232C0L1117266865&lt;1
-- MUNOZ&lt;BARRETO&lt;</t>
+          <t xml:space="preserve">*&amp;&amp;?&amp;? MA
+a R be Za
+' &gt; A NO uA NE Da el
+ ICCOLO72680478644024&lt;&lt;&lt;&lt;&lt;&lt;&lt;&lt;&lt;&lt;
+9512243F3501232COL1117266865&lt;1
+MUNOZ&lt;BARRETO&lt;&lt;NATALI&lt;&lt;&lt;&lt;&lt;&lt;&lt;&lt;&lt;
+h | u
+Powered by CamScanner
+</t>
         </is>
       </c>
     </row>
@@ -1910,13 +2244,17 @@
           <t>34</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>17660162</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>PINEDA GONZALEZ AN PABLO EMILIO</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
@@ -1927,15 +2265,11 @@
       <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">REPÚBLICA DE COLOMBIA
-ENTIFICACIÓN PERSONAL eae &lt;a
-PINEDA CONZALE? 9. ===&gt; a... ta
-REPÚBLICA DE COLOMBIA |
-TIBIA
-¡IDENTIFICACIÓN PERSONAL - De
-PINEDA GONZALEZ 11. == MB.
-$. Se3tl] | a a ds oe
-$ igs 8: ~ HS AN Nico an
-A AA a i aA aver Ren
+IDENTIFICACIÓN PERSON¿L e |
+s 17.660.162 2F S
+PINEDA GONZALEZ an . *
+PABLO EMILIO _ a
+NOMBRES ; | a o gl
 </t>
         </is>
       </c>
@@ -1958,43 +2292,33 @@
           <t>30-MAY-1965</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>MAY</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>30-MAY-1965</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>ZEN</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESOO FECHA DE NACIMIENTO 30-MAY-1965
-ZEN LUGAR DE NACIMIENTO
-aC i167 os &amp;
-Bas ESTATURA ae mu sexo |
-to, IS pp | *
-EX: FECHA DE NACIMIENTO 30-MAY-1965
-| ¿IE (CAQUETA)
-ZEN SE LUGAR DE NACIMIENTO
-lg SS
-SS ESTATURA G.S. RH |
-e 31-MAY-1983 EL DONCELLO ]
-FECHA Y LUGAR DE EXPEDICIÓN
-INDICE DERECHO bata a </t>
+          <t xml:space="preserve">— \.\‘\. -
+_ NN FECHA DE NACIMIENTO 30-MAY-1965
+¿%Q LUGAR DE NACIMIENTO
+— 31-MAY-1983 EL DONCELLO —
+FECHA Y LUGAR DE EXPEDICIÓN —
+NDICE DERECHO REGISTRADOR w:áw_
+‘ ALEXANDER VEGA ROCHA
+; . "u | .'l l‘l“ l o ‘u E TE 8 "NE
+MA EE E ñ \ ; . NE 1a " dl e Y i
+A-4400500-01269103-M-0017660162-20211126 0076884015A 1 55446520
+</t>
         </is>
       </c>
     </row>
@@ -2009,8 +2333,16 @@
           <t>1010206409</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SAENZ TOVAR</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LAURA YOLLYS</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
@@ -2020,15 +2352,17 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t xml:space="preserve">REPUBLICA DE COLOMBIA
- ADENTIFICACION PERSONAL
-ey J CEDULA DE CIUDADANIA
+          <t xml:space="preserve">-
 REPUBLICA DE COLOMBIA
-2 ¡ADENTIFICACION PERSONAL
-ce: CEDULA DE CIUDADANIA
-“numero 1.01 0.206.409 A
-APELLIDOS e === =&gt; ma
-SNUAURA VOLLYS. P 404/22: y
+IDENTIFICACION PERSONAL
+CEDULA DE CIUDADANIA
+NUMERO” 1.010.206.409
+SAENZ TOVAR
+APELLIDOS
+LAURA YOLLYS
+| NOMBRES
+| FIRMA
+Scanned with CamScanner
 </t>
         </is>
       </c>
@@ -2051,21 +2385,25 @@
           <t>15-ENE-1993</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>ENE</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>164</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>15-ENE-1993</t>
+          <t>01-FEB-2011</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2075,17 +2413,26 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t xml:space="preserve">LE ER FECHA DE NACIMIENTO 15-ENE-1993
-ZA LERIDA *
-WA (TOLIMA) =
-err LUGAR DE/NACIMIENTO
-BS SST ESTATURA 8 — a sfRH SEXO
-: AOS REE AN
-{A= FECHA DE NACIMIENTO -1 9-ENE-1993
-ATI 7 LUGAR DE NACIMIENTO
-REA === ESTATURA: |). GO SPRH SEXO
-SADA 01-FEB-2011 BOGOTA D.C | %
-FECHA Y LUGAR DE EXPEDICION fata </t>
+          <t xml:space="preserve">: NE Aº_._-r'- '.
+í : Q“E%cg&amp;¿ FECHA DE NACIMIENTO 15-ENE-1993
+UN (TOLIMA)
+Da LUGAR DE NACIMIENTO
+— N@@; 1.64 B+ F
+l=a = O ESTATURA G.S7RH SEXO
+A — ’xj-"‘ﬂv‘
+S= 01-FEB-2011 BOGOTA D.C 4
+FECHA Y LUGAR DE EXPEDICION/M/M-M/“"‘“j i
+INDICE DERECHO L REGISTRADOR NACIONAL
+CARLOS ARIEL SANCHEZ TORRES
+' 1 = = 2 , 1 a
+' : ' ' i L .
+F: Pl | ;
+. | N ' l ' i
+. y ! I
+? ; " l . 1 , 1 * .
+P-1500150-00284635-F-1010206409-20110317 0026177578A 1 36049524
+Scanned with CamScanner
+</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2442,12 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>436345</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
@@ -2111,19 +2458,39 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>PUBLICA DE COLOMBIA ¿M7
-CEDULA DÉ CIUDADANÍA - paces PR &gt;
-29 DANIA ER ag x
-NUMERO 436.345 . oh de tite 1.1 q ee 5
-Re fo Fee rs EN Bese e AE ‘
-o. - A Ñ LR &gt; 6 . Ea . a 7 &gt;
-ae EA A IÓ ts E
-. : wy a - + , SN 4
-REPUBLICA DE COLOMBIA me
-« “d ye . ‘ o 9 y ¿ 3
-IDENTIFICAC ms o La
-ION PERSONAL 2: A 2
-i $ d</t>
+          <t>_ T E - E =
+. . - iii
+- . ' v — - -
+* ; " s -
+'. ' _.. » E . - . -
+* a .- , "' ....o .7. ¿ . - - . ?
+' ( &gt; \ D "y ,
+REPUBLICA DE COLOMBIA + .. - — E
+, - o o‘\{\. ((. ‘. .\." 2 . :
+IDENTIFICACION PERSONAL .- --
+s - . 0”‘.- » l 4 s
+".. — - .l
+' ". * » . *. '
+CEDULA DE CIUDADANIA =£ 21£ s
+¢ E - '
+_ .¡ .» i.; ,» " , —
+r ' "K .,. - . .. . a
+s " » ' » ' , * m de e |
+NUMERO 29. : RA e E - —
+de ‘; * « . - 2 5 a s Ar - ...' - “J‘q -
+. r a ) ‘_- l‘. . ; £ 1 ) Y
+- l a - , . | ". » r ;. ; " ,
+“ 4 ;‘l‘ -P'. &lt; r .-,‘5' v € '-.¡t..
+" u"(l' ,.¡ 1\‘ , , I . - ‘ .,,' I.. o .. &amp; \ ; .—_ -
+” 4 - a- . &amp; TH . . » e "a =
+.t '¡3.';'.'. '. '-' A » 0; - * H' - 5 J . ; '. “ * . -
+N - ,‘T’ E ‘. , q v\' ,\‘F q .l‘ ) - ‘.' 7 — - ' « o
+3 - ¢ rEC” . E , si , !
+' .' 54 o &amp; I’r”‘ A% aa "-‘U'(‘.( "‘ “. (‘7.,'~ .l. a Á ' 3 ' e Í. )
+. , . [ . i A E A ,
+, . AQ É E TE N TA | . | (
+MONICA NN TI — ….
+P y J , —"_ Ul % ' )““.l..,</t>
         </is>
       </c>
     </row>
@@ -2140,49 +2507,43 @@
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>25-AGO-1984</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>10-ABR-2003</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
         <is>
           <t>CALI</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>25-AGO-1984</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>CALI</t>
-        </is>
-      </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>NG ss aN FECHA DE NACIMIENTO. 25-AGO-1984 ~
-MENOS. CALIMA
-le SN (VALLE)
-(e ' LUGAR DE NACIMIENTO | |
-IÓN 1.65 a
-XV ESTATURA QS. RH Ex
-UESA&gt;===AA 1-ABREZODICALIMA 2. O)
-e» DENACIMIENTO 25-AGO-1984 —
-CO. CALIMA
-le SS (VALLE)
-a LUGAR DE NACIMIENTO i
-YW“ 1.65 Oa ES
-ESTATURA, (G.S. RH SEXO
-=&gt; 10-ABR-200</t>
+          <t xml:space="preserve">r T - —
+E;ECHA DE NACIMIENTO 25-AGO0-1984
+/ E 3&amp; CALIMA
+TNE VALLE
+(@\ N (l_UGAR D)E NACIMIENTO —
+' &amp;g_—_ Eg'fAºá?A G%; RH sg.:xo
+| á”%?í _ 10-ABR-2003 CALIMA . —
+JW/ÁI//% FECHA Y LUGAR DE EXPEDICION CM
+INDICE DERECHO RESQ'AS z;rei’\a?@qq’(\'i —
+o yo e U b AT N AL A o BB A N an A E
+N
+A AE d O i O BT AE a PA T A N "3"”' |
+e NA *¡¡,'¡ ¡i "42»3,'. Y E}‘W :} aal A .gg}\ )
+¥ NN "P INE ha Y ; ¡..' , a -
+A-4401000-67 152491-F-0029436345-20060922 0301906264A 03 993251151
+</t>
         </is>
       </c>
     </row>
@@ -2204,18 +2565,28 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>A A ee e. ES te o
-E dr tr | ceca Wen ab
-“AREPÚBLICA DE COLOMBIA - RE We
-tu ADE ACION PERSONAL — bl
-: 133 PITS &gt; be be FAA
-A fe 7 y See Ps
-. A Es 4 po a A E 7 ‘ xe = ae ;
-. ES 5 ? * j e Des : we &gt; ves
-Sg See SUE 53 :
-PES Ss wae. te 24 EN &gt; 3 Pa &gt; ud §
-qe Ay "se \ AO A |
-a M : hs * E 17 qe &gt; MEA Vs €</t>
+          <t xml:space="preserve">C jj ML R + | del
+s - o P » v£ ae
+— REPUBLICA DE COLOMBIA
+A . £ o
+£ i _._ -y . . - &gt;
+: _'4. A ? ':,,_. P 5 - . ; . - . , -
+- — “- , ‘J_ ñ — v‘ - 4 ' -
+. &gt; ig 4‘_’_" &gt; 2 - 1— 4*‘7- . 3 A
+“Mudrdn 7 " — —
+] ' — % . - o :—-º 2o E Y o u — * y
+e ; y . = N 1 g # € í » Ml R
+i E ".. - - — 3 . a = eS|
+p L | —| a TE * i)
+— f E ¿ - e ea
+" .'p' o S 2240 = - … Y ¥ Esc ¿ A _º-_'º'ñ_ N , 7 M e g ’, J
+; s —.,_ % -.. . - — . RA — » A 7 % x5 it
+á — PLISTICA L1 ' i A
+— _ — “ ". Ta T A M :
+F ae yS EEO ye A ,
+L _‘ T = - - É 77 m C A A /
+: E CamScanner’;
+</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2596,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>00678622</t>
+        </is>
+      </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
@@ -2233,44 +2608,39 @@
           <t>22-NOV-1984</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>05-DIC-2002</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>IBAGUE</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>22-NOV-1984</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>IBAGUE</t>
-        </is>
-      </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>¿ES FECHA DE NACIMIENTO 22-NOV-1984
-ES IBAGUE «
-NN (TOLIMA)
-NN LUGAR DE:NACIMIENTO
-no 171. 0 Mo
-=&gt; ESTATURA: =. GS, AH SEXO
-a De e: $ , Ar FLA ARAS ds A más
-ES FECHA DE NACIMIENTO 22-NOV-1984
-LES IBAGUE 4”
-GN (TOLIMA) |
-HN \ LUGAR DE:NACIMIENTO
-SS “1.71 O+ M
-SS ESTATURA G.S, RH SEXO
-: a 0 05-DIC-20</t>
+          <t xml:space="preserve">AN FECHA DE NACIMIENTO — 22-NOV-1984
+7 (TOLIMA)
+),, }/('f \ LUGAR DE NACIMIENTO
+/I/KK
+— ESTATURA G.S. AH SEXO
+05-DIC-2002 IBAGUE f
+FECHA Y LUGAR DE EXPEDICION / u s.st. o /o=
+INDICE DERECHO REGISTRADOR NACIONAL
+CARLOS ARIEL SÁNCHEZ TORRES
+It A o IS NA ERPO y Ta. A (| e
+’, 4 "*'Í': .’,) | .'f*\-‘tnﬂ I“'. TV AP '.tru".'º o Ú
+_ A-2900100-00678622-M-0093236687-20150316 0043588047A 1 6383248747
+</t>
         </is>
       </c>
     </row>
@@ -2280,11 +2650,7 @@
           <t>42</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>0007880092</t>
-        </is>
-      </c>
+      <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
@@ -2292,35 +2658,17 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>02-ENE-1969</t>
-        </is>
-      </c>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>A AA A re. Ae memetanee
-gre, a a PLC &gt;,
-te “PBs
-* eal ae am
-ne FEDLILA DI ers a ee BERT
-Pag a E ¿904 da . y
-Pp, 2 ye
-3 J a ne :
-BR | ie” &lt;q.
-j . i ae 75 t Fiat
-CT A ™
-P in" e "
-' Acce $
-numero 7.556 aa a
-RODRIGUEZ ol. AH
-APELLIDOS
-dl 7 Pe d 7 e A =
-pro di 02-ENE-1969 si
-Hise AN = P
-FECMA Y |
-INDICE</t>
+          <t xml:space="preserve">i'_'%
+.“’.
+!Í)
+í 88 0. -
+4 " - :
+- *
+</t>
         </is>
       </c>
     </row>
